--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra3812196a5814133"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R505bb159e1ef4418"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R505bb159e1ef4418"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6c676b3522de4a80"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6c676b3522de4a80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb777ffaaf48f4ac8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb777ffaaf48f4ac8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2846ee5725d34e82"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2846ee5725d34e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0a199056e9594e20"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0a199056e9594e20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfeaa09a8c06b47bc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfeaa09a8c06b47bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rff7f735c01aa4f8d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rff7f735c01aa4f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb35807cb4c5e4906"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb35807cb4c5e4906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4a6c22d93f104098"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4a6c22d93f104098"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R56a55892a4e946de"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_ListFromRange/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R56a55892a4e946de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8437e7fba9b24ea1"/>
   </x:sheets>
 </x:workbook>
 </file>
